--- a/projects/paper-02/03-screen/数据_3_全文筛选待下载列表.xlsx
+++ b/projects/paper-02/03-screen/数据_3_全文筛选待下载列表.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,8 +40,24 @@
     <font>
       <color rgb="00000000"/>
     </font>
+    <font>
+      <color rgb="00276221"/>
+    </font>
+    <font>
+      <color rgb="009C0006"/>
+    </font>
+    <font>
+      <color rgb="00595959"/>
+    </font>
+    <font>
+      <strike val="1"/>
+      <color rgb="00595959"/>
+    </font>
+    <font>
+      <color rgb="007D6608"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +77,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFCCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -90,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -121,6 +147,21 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -581,9 +622,9 @@
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I2" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -620,9 +661,9 @@
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -659,9 +700,9 @@
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -698,9 +739,9 @@
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -737,9 +778,9 @@
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -776,9 +817,9 @@
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>排除-E3</t>
         </is>
       </c>
     </row>
@@ -815,9 +856,9 @@
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -854,9 +895,9 @@
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -893,9 +934,9 @@
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -932,9 +973,9 @@
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -971,9 +1012,9 @@
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I12" s="12" t="inlineStr">
+        <is>
+          <t>排除-E2</t>
         </is>
       </c>
     </row>
@@ -1010,9 +1051,9 @@
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -1049,9 +1090,9 @@
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I14" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -1088,9 +1129,9 @@
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -1127,9 +1168,9 @@
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I16" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -1166,9 +1207,9 @@
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -1205,9 +1246,9 @@
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I18" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -1244,9 +1285,9 @@
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -1283,9 +1324,9 @@
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -1322,9 +1363,9 @@
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -1361,9 +1402,9 @@
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>排除-E2</t>
         </is>
       </c>
     </row>
@@ -1400,9 +1441,9 @@
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -1439,9 +1480,9 @@
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -1478,9 +1519,9 @@
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -1517,9 +1558,9 @@
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I26" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -1556,9 +1597,9 @@
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -1595,9 +1636,9 @@
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I28" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -1634,9 +1675,9 @@
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -1673,9 +1714,9 @@
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -1712,9 +1753,9 @@
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I31" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -1751,9 +1792,9 @@
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I32" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -1790,9 +1831,9 @@
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -1829,9 +1870,9 @@
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I34" s="12" t="inlineStr">
+        <is>
+          <t>排除-E1</t>
         </is>
       </c>
     </row>
@@ -1868,9 +1909,9 @@
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -1907,9 +1948,9 @@
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I36" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -1946,9 +1987,9 @@
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I37" s="12" t="inlineStr">
+        <is>
+          <t>排除-E4</t>
         </is>
       </c>
     </row>
@@ -1985,9 +2026,9 @@
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I38" s="12" t="inlineStr">
+        <is>
+          <t>排除-E1</t>
         </is>
       </c>
     </row>
@@ -2024,9 +2065,9 @@
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I39" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -2063,9 +2104,9 @@
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I40" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -2102,9 +2143,9 @@
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I41" s="12" t="inlineStr">
+        <is>
+          <t>排除-E2</t>
         </is>
       </c>
     </row>
@@ -2141,9 +2182,9 @@
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I42" s="15" t="inlineStr">
+        <is>
+          <t>待确认-需下载</t>
         </is>
       </c>
     </row>
@@ -2180,9 +2221,9 @@
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I43" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -2219,9 +2260,9 @@
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I44" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -2258,9 +2299,9 @@
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I45" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -2297,9 +2338,9 @@
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I46" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -2336,9 +2377,9 @@
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I47" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -2375,9 +2416,9 @@
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I48" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -2414,9 +2455,9 @@
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I49" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -2453,9 +2494,9 @@
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I50" s="15" t="inlineStr">
+        <is>
+          <t>待确认-需下载</t>
         </is>
       </c>
     </row>
@@ -2492,9 +2533,9 @@
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I51" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -2531,9 +2572,9 @@
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr"/>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I52" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -2570,9 +2611,9 @@
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I53" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -2609,9 +2650,9 @@
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I54" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -2648,9 +2689,9 @@
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I55" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -2687,9 +2728,9 @@
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I56" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -2726,9 +2767,9 @@
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I57" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -2765,9 +2806,9 @@
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I58" s="12" t="inlineStr">
+        <is>
+          <t>排除-E1</t>
         </is>
       </c>
     </row>
@@ -2804,9 +2845,9 @@
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I59" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -2843,9 +2884,9 @@
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -2882,9 +2923,9 @@
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I61" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -2921,9 +2962,9 @@
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I62" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -2960,9 +3001,9 @@
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I63" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -2999,9 +3040,9 @@
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I64" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -3038,9 +3079,9 @@
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I65" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -3077,9 +3118,9 @@
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr"/>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I66" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -3116,9 +3157,9 @@
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I67" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -3155,9 +3196,9 @@
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -3194,9 +3235,9 @@
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -3233,9 +3274,9 @@
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I70" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -3271,10 +3312,14 @@
           <t>保留2</t>
         </is>
       </c>
-      <c r="H71" s="4" t="inlineStr"/>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>10.1111/desc.12839</t>
+        </is>
+      </c>
+      <c r="I71" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -3311,9 +3356,9 @@
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I72" s="15" t="inlineStr">
+        <is>
+          <t>待确认-需下载</t>
         </is>
       </c>
     </row>
@@ -3350,9 +3395,9 @@
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -3389,9 +3434,9 @@
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I74" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -3428,9 +3473,9 @@
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I75" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -3467,9 +3512,9 @@
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I76" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -3506,9 +3551,9 @@
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr"/>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I77" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -3544,10 +3589,14 @@
           <t>保留2</t>
         </is>
       </c>
-      <c r="H78" s="4" t="inlineStr"/>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>10.1111/desc.12344</t>
+        </is>
+      </c>
+      <c r="I78" s="15" t="inlineStr">
+        <is>
+          <t>待确认-需下载</t>
         </is>
       </c>
     </row>
@@ -3584,9 +3633,9 @@
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I79" s="12" t="inlineStr">
+        <is>
+          <t>排除-E2</t>
         </is>
       </c>
     </row>
@@ -3623,9 +3672,9 @@
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I80" s="12" t="inlineStr">
+        <is>
+          <t>排除-E2</t>
         </is>
       </c>
     </row>
@@ -3662,9 +3711,9 @@
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr"/>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I81" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -3701,9 +3750,9 @@
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -3740,9 +3789,9 @@
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I83" s="12" t="inlineStr">
+        <is>
+          <t>排除-E2</t>
         </is>
       </c>
     </row>
@@ -3779,9 +3828,9 @@
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I84" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -3818,9 +3867,9 @@
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I85" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -3857,9 +3906,9 @@
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I86" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -3896,9 +3945,9 @@
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I87" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -3935,9 +3984,9 @@
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I88" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -3974,9 +4023,9 @@
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I89" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -4013,9 +4062,9 @@
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I90" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -4052,9 +4101,9 @@
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I91" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -4091,9 +4140,9 @@
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr"/>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I92" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -4130,9 +4179,9 @@
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I93" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -4169,9 +4218,9 @@
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I94" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -4208,9 +4257,9 @@
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I95" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -4247,9 +4296,9 @@
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I96" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -4286,9 +4335,9 @@
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I97" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -4325,9 +4374,9 @@
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
-      <c r="I98" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I98" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -4364,9 +4413,9 @@
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I99" s="12" t="inlineStr">
+        <is>
+          <t>排除-E2</t>
         </is>
       </c>
     </row>
@@ -4403,9 +4452,9 @@
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I100" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -4442,9 +4491,9 @@
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I101" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -4481,9 +4530,9 @@
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
-      <c r="I102" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I102" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -4520,9 +4569,9 @@
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I103" s="15" t="inlineStr">
+        <is>
+          <t>待确认-需下载</t>
         </is>
       </c>
     </row>
@@ -4559,9 +4608,9 @@
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I104" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -4569,7 +4618,7 @@
       <c r="A105" s="2" t="n">
         <v>104</v>
       </c>
-      <c r="B105" s="3" t="inlineStr">
+      <c r="B105" s="13" t="inlineStr">
         <is>
           <t>Socioeconomic status effects on children's vocabulary brain development</t>
         </is>
@@ -4597,10 +4646,14 @@
           <t>保留2</t>
         </is>
       </c>
-      <c r="H105" s="4" t="inlineStr"/>
-      <c r="I105" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="H105" s="4" t="inlineStr">
+        <is>
+          <t>10.1016/j.avb.2021.101702</t>
+        </is>
+      </c>
+      <c r="I105" s="14" t="inlineStr">
+        <is>
+          <t>已撤稿</t>
         </is>
       </c>
     </row>
@@ -4637,9 +4690,9 @@
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I106" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -4676,9 +4729,9 @@
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I107" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -4715,9 +4768,9 @@
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr"/>
-      <c r="I108" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I108" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -4754,9 +4807,9 @@
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
-      <c r="I109" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I109" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -4793,9 +4846,9 @@
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I110" s="15" t="inlineStr">
+        <is>
+          <t>待确认-需下载</t>
         </is>
       </c>
     </row>
@@ -4831,10 +4884,14 @@
           <t>不确定</t>
         </is>
       </c>
-      <c r="H111" s="7" t="inlineStr"/>
-      <c r="I111" s="5" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="H111" s="7" t="inlineStr">
+        <is>
+          <t>10.1080/09297049.2021.1879766</t>
+        </is>
+      </c>
+      <c r="I111" s="12" t="inlineStr">
+        <is>
+          <t>排除-E1</t>
         </is>
       </c>
     </row>
@@ -4871,9 +4928,9 @@
         </is>
       </c>
       <c r="H112" s="7" t="inlineStr"/>
-      <c r="I112" s="5" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I112" s="12" t="inlineStr">
+        <is>
+          <t>排除-E2</t>
         </is>
       </c>
     </row>
@@ -4910,9 +4967,9 @@
         </is>
       </c>
       <c r="H113" s="7" t="inlineStr"/>
-      <c r="I113" s="5" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I113" s="12" t="inlineStr">
+        <is>
+          <t>排除-E2</t>
         </is>
       </c>
     </row>
@@ -4949,9 +5006,9 @@
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr"/>
-      <c r="I114" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I114" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -4988,9 +5045,9 @@
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
-      <c r="I115" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I115" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -5027,9 +5084,9 @@
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr"/>
-      <c r="I116" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I116" s="12" t="inlineStr">
+        <is>
+          <t>排除-E2</t>
         </is>
       </c>
     </row>
@@ -5066,9 +5123,9 @@
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
-      <c r="I117" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I117" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -5105,9 +5162,9 @@
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
-      <c r="I118" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I118" s="12" t="inlineStr">
+        <is>
+          <t>排除-E8</t>
         </is>
       </c>
     </row>
@@ -5144,9 +5201,9 @@
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
-      <c r="I119" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I119" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -5183,9 +5240,9 @@
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
-      <c r="I120" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I120" s="12" t="inlineStr">
+        <is>
+          <t>排除-E2</t>
         </is>
       </c>
     </row>
@@ -5222,9 +5279,9 @@
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
-      <c r="I121" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I121" s="15" t="inlineStr">
+        <is>
+          <t>待确认-需下载</t>
         </is>
       </c>
     </row>
@@ -5261,9 +5318,9 @@
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
-      <c r="I122" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I122" s="12" t="inlineStr">
+        <is>
+          <t>排除-E4</t>
         </is>
       </c>
     </row>
@@ -5300,9 +5357,9 @@
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
-      <c r="I123" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I123" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -5339,9 +5396,9 @@
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
-      <c r="I124" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I124" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -5378,9 +5435,9 @@
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr"/>
-      <c r="I125" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I125" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -5417,9 +5474,9 @@
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
-      <c r="I126" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I126" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -5456,9 +5513,9 @@
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
-      <c r="I127" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I127" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -5495,9 +5552,9 @@
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
-      <c r="I128" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I128" s="12" t="inlineStr">
+        <is>
+          <t>排除-E1</t>
         </is>
       </c>
     </row>
@@ -5534,9 +5591,9 @@
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
-      <c r="I129" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I129" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -5573,9 +5630,9 @@
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
-      <c r="I130" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I130" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -5612,9 +5669,9 @@
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr"/>
-      <c r="I131" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I131" s="12" t="inlineStr">
+        <is>
+          <t>排除-E8</t>
         </is>
       </c>
     </row>
@@ -5651,9 +5708,9 @@
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
-      <c r="I132" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I132" s="12" t="inlineStr">
+        <is>
+          <t>排除-E2</t>
         </is>
       </c>
     </row>
@@ -5690,9 +5747,9 @@
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
-      <c r="I133" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I133" s="11" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
     </row>
@@ -5729,9 +5786,9 @@
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr"/>
-      <c r="I134" s="2" t="inlineStr">
-        <is>
-          <t>待下载</t>
+      <c r="I134" s="12" t="inlineStr">
+        <is>
+          <t>排除-E8</t>
         </is>
       </c>
     </row>
